--- a/Peliculas.xlsx
+++ b/Peliculas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -666,7 +666,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,931 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Blue velvet</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1986</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>David lynch</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>21 gramos</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2003</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Alejandro gonzález iñárritu</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>El renacido</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Alejandro gonzález iñárritu</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Babel</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2006</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Alejandro gonzález iñárritu</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ciudad de dios</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2002</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Fernando meirelles, kátia lund</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ciudadano kane</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1941</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Orson welles</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Casa blanca</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1942</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Michael curtiz</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Scarface</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1983</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Brian de palma</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Serpico</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1973</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sidney lumet</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>El irlandes</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Martin scorsese</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Perfume de mujer</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1992</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Martin brest</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Heat</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1995</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Michael mann</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Dog day afternoon</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1975</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Sidney lumet</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>The deer hunter</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1978</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Michael cimino</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Raging bull</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Martin scorsese</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Goodfellas</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Martin scorsese</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Casino</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1995</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Martin scorsese</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Donnie brasco</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1997</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Mike newell</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>La isla siniestra</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Martin scorsese</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Los infiltrados</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2006</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Martin scorsese</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>La última tentación de cristo</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1988</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Martin scorsese</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>El faro</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Robert eggers</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>The northman</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Robert eggers</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>The witch</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Robert eggers</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Nosferatu</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Robert eggers</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>La ventana indiscreta</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1954</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Alfred hitchcock</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Vertigo</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1958</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Alfred hitchcock</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>No country for old men</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ethan coen, joel coen</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Troya</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2004</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Wolfgang petersen</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Cruzada</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2005</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ridley scott</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Pulp fiction</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1994</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Quentin tarantino</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Reservoir dogs</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1992</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Quentin tarantino</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Blade runner</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1982</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ridley scott</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Chinatown</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1974</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Roman polanski</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>El halcón maltes</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1941</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>John huston</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>La reina africana</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1951</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>John huston</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>El tesoro de la sierra madre</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1948</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>John huston</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Mientras la ciudad duerme</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1950</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>John huston</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Huracán de pasiones</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1948</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>John huston</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>El hombre que sería rey</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1975</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>John huston</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Los inadaptados</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1961</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>John huston</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>La noche de la iguana</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1964</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>John huston</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>El aviador</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>2004</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Martin scorsese</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Paris, texas</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1984</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Wim wenders</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>El séptimo sello</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1957</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ingmar bergman</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senderos de gloria</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1957</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Stanley kubrick</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
